--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M266"/>
+  <dimension ref="A1:M267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6483.53</v>
+        <v>6428.62</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>851.8099999999999</v>
+        <v>847.4299999999999</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2711.33</v>
+        <v>2684.27</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2638.2</v>
+        <v>2623.78</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2953.07</v>
+        <v>2920.17</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3531.09</v>
+        <v>3511.76</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>750.3</v>
+        <v>752.98</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11250.41</v>
+        <v>11372.77</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2242.08</v>
+        <v>2249.46</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2342.15</v>
+        <v>2349.85</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6230.51</v>
+        <v>6251</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1791.3</v>
+        <v>1799.64</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9788.82</v>
+        <v>9834.4</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4816.48</v>
+        <v>4838.91</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1579.08</v>
+        <v>1590.46</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3654.07</v>
+        <v>3680.42</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3013.54</v>
+        <v>3035.27</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1646.06</v>
+        <v>1643.14</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2231.92</v>
+        <v>2222.72</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16905.26</v>
+        <v>16844.64</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3261.58</v>
+        <v>3254.52</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1056.13</v>
+        <v>1053.85</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3505.15</v>
+        <v>3490.45</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3942.59</v>
+        <v>3926.06</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>761.41</v>
+        <v>758.22</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2593.37</v>
+        <v>2563.36</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5525.1</v>
+        <v>5461.16</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>807.63</v>
+        <v>800.79</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1701.34</v>
+        <v>1699.97</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3426.18</v>
+        <v>3423.43</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7691.92</v>
+        <v>7712.32</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6157.74</v>
+        <v>6174.07</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2293.97</v>
+        <v>2300.06</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2619.06</v>
+        <v>2622.41</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10079.17</v>
+        <v>10092.09</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2098.96</v>
+        <v>2121.47</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>11130.7</v>
+        <v>11273.73</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3761.17</v>
+        <v>3706.97</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6251.78</v>
+        <v>6239.47</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>13305.77</v>
+        <v>13279.56</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2644.48</v>
+        <v>2644.5</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6610.54</v>
+        <v>6619.72</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>14545.57</v>
+        <v>14565.77</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8336.879999999999</v>
+        <v>8348.459999999999</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5102</v>
+        <v>5109.09</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5537.1</v>
+        <v>5544.79</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4187.24</v>
+        <v>4184.38</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5825.29</v>
+        <v>5821.31</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4522.08</v>
+        <v>4518.99</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>4236.87</v>
+        <v>4214.49</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3188.89</v>
+        <v>3168.91</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1875.53</v>
+        <v>1863.78</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1146.97</v>
+        <v>1139.78</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3781.25</v>
+        <v>3806.03</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2524.27</v>
+        <v>2558.26</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2328.94</v>
+        <v>2360.3</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4615.25</v>
+        <v>4677.41</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1359.76</v>
+        <v>1378.07</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1641.78</v>
+        <v>1666.77</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3450.34</v>
+        <v>3502.87</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5206.67</v>
+        <v>5338.29</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2465.82</v>
+        <v>2540.59</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2837.8</v>
+        <v>2923.85</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2129.77</v>
+        <v>2135.94</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6951.8</v>
+        <v>6971.94</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3858.16</v>
+        <v>3869.33</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2399.55</v>
+        <v>2411.94</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4588.71</v>
+        <v>4612.41</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1860.86</v>
+        <v>1865.97</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2345.77</v>
+        <v>2361.22</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2461.27</v>
+        <v>2477.48</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3018.46</v>
+        <v>3038.34</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>947.4299999999999</v>
+        <v>955.86</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1325.54</v>
+        <v>1337.34</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>904.49</v>
+        <v>912.55</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>831.4</v>
+        <v>838.8</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1008.67</v>
+        <v>1017.66</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>809.67</v>
+        <v>816.88</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2036.27</v>
+        <v>2054.41</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2347.47</v>
+        <v>2368.38</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>14310.66</v>
+        <v>14438.12</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>6929.61</v>
+        <v>6991.33</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5218.32</v>
+        <v>5264.8</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1762.5</v>
+        <v>1778.2</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1778.75</v>
+        <v>1794.59</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3307.05</v>
+        <v>3336.51</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1533.71</v>
+        <v>1531.08</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2490.13</v>
+        <v>2485.86</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1303.33</v>
+        <v>1301.98</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>896.23</v>
+        <v>895.3</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>15311.12</v>
+        <v>15295.33</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1935.15</v>
+        <v>1933.16</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3002.27</v>
+        <v>2999.18</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1472.44</v>
+        <v>1470.92</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>815.03</v>
+        <v>814.1900000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1557.49</v>
+        <v>1555.88</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4524.28</v>
+        <v>4491.87</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1314.38</v>
+        <v>1304.97</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>840.87</v>
+        <v>834.84</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1982.63</v>
+        <v>1968.43</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1436.44</v>
+        <v>1426.15</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4831.34</v>
+        <v>4796.73</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2620.27</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6864</v>
+        <v>6826.62</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>815.09</v>
+        <v>810.28</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2371.72</v>
+        <v>2357.74</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>837.99</v>
+        <v>832.9</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2577.95</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6423.61</v>
+        <v>6610.2</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>14823.08</v>
+        <v>15253.64</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3413.12</v>
+        <v>3512.26</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3212.17</v>
+        <v>3305.48</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>7138.12</v>
+        <v>7345.46</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7021.24</v>
+        <v>7225.18</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>31003.99</v>
+        <v>31904.54</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1738.42</v>
+        <v>1788.91</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1613.2</v>
+        <v>1660.06</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2275.22</v>
+        <v>2284.19</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5823.51</v>
+        <v>5846.47</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>20148.02</v>
+        <v>20227.46</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5053.6</v>
+        <v>5073.52</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>6411.1</v>
+        <v>6436.38</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2302.2</v>
+        <v>2307.86</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>6006.94</v>
+        <v>5929.6</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3926.2</v>
+        <v>3875.66</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3215.2</v>
+        <v>3173.81</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4661.08</v>
+        <v>4601.07</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3804.92</v>
+        <v>3755.93</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>8995.52</v>
+        <v>8879.709999999999</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1041.02</v>
+        <v>1027.62</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1572</v>
+        <v>1551.76</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2747.39</v>
+        <v>2712.02</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2500.45</v>
+        <v>2468.26</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>12356.4</v>
+        <v>12269.2</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>11189.93</v>
+        <v>11110.96</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3131.02</v>
+        <v>3108.93</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>5859.27</v>
+        <v>5951.05</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6178.91</v>
+        <v>6275.7</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1019.74</v>
+        <v>1035.72</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1437.49</v>
+        <v>1437.42</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>7201.25</v>
+        <v>7200.88</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1168.08</v>
+        <v>1168.02</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2588.32</v>
+        <v>2588.19</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2447.51</v>
+        <v>2436.57</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>7182.16</v>
+        <v>7150.04</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1544.57</v>
+        <v>1537.66</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2717.63</v>
+        <v>2705.47</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4110.46</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>792.92</v>
+        <v>796.2</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>12881.18</v>
+        <v>12845.64</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>943.74</v>
+        <v>929.67</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2887</v>
+        <v>2870.42</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1960.79</v>
+        <v>1952.34</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>4285.49</v>
+        <v>4193.29</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1301.96</v>
+        <v>1278.35</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>7494.94</v>
+        <v>7359.02</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3024.59</v>
+        <v>2969.74</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2453.28</v>
+        <v>2408.79</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2202.85</v>
+        <v>2209.27</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2004.37</v>
+        <v>2010.2</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>13549.55</v>
+        <v>13605.86</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3122.24</v>
+        <v>3117.02</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>6112.78</v>
+        <v>6102.56</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1912.72</v>
+        <v>1936.26</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>4578.97</v>
+        <v>4638.72</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1217.6</v>
+        <v>1233.49</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3164.1</v>
+        <v>3205.4</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>801.23</v>
+        <v>820.95</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1547.04</v>
+        <v>1576.3</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6496.83</v>
+        <v>6619.7</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>6667.25</v>
+        <v>6743.07</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2536.16</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>3077.37</v>
+        <v>3112.37</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>5963.11</v>
+        <v>6030.93</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>4158.19</v>
+        <v>4195.64</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1209.5</v>
+        <v>1220.39</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5635.32</v>
+        <v>5671.37</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>35005.12</v>
+        <v>35229.01</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>794.54</v>
+        <v>799.62</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>803.4400000000001</v>
+        <v>805.96</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1464.71</v>
+        <v>1469.32</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2800.7</v>
+        <v>2812.31</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>7170.8</v>
+        <v>7185.66</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>11339.57</v>
+        <v>11290.85</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>10604.55</v>
+        <v>10460.38</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2979</v>
+        <v>2953.6</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4994.95</v>
+        <v>5021.84</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>6470.44</v>
+        <v>6542.8</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>4017.18</v>
+        <v>4047.61</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1054.57</v>
+        <v>1062.56</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1263.39</v>
+        <v>1272.96</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>7647.81</v>
+        <v>7705.74</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3274.75</v>
+        <v>3287.15</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2386.26</v>
+        <v>2395.3</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3812.74</v>
+        <v>3848.97</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1050.17</v>
+        <v>1060.15</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3720.98</v>
+        <v>3756.33</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>2518.77</v>
+        <v>2542.7</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>787.9</v>
+        <v>780.05</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2140.08</v>
+        <v>2118.74</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2144.86</v>
+        <v>2123.47</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1419.72</v>
+        <v>1405.56</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1310.23</v>
+        <v>1297.17</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3027.24</v>
+        <v>2994.31</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4050.91</v>
+        <v>4006.84</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>4032.78</v>
+        <v>3988.91</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2319.45</v>
+        <v>2314.18</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1295.08</v>
+        <v>1292.14</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>6714.84</v>
+        <v>6698.26</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3379.95</v>
+        <v>3371.6</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2991.8</v>
+        <v>3006.5</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>21638.1</v>
+        <v>21706.97</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2176.14</v>
+        <v>2187.71</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2886.11</v>
+        <v>2915.46</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>7920.1</v>
+        <v>8000.64</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>803.13</v>
+        <v>810.67</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1533.26</v>
+        <v>1511.5</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1969.49</v>
+        <v>1957.28</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2169.74</v>
+        <v>2202.04</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>985.6</v>
+        <v>1004.33</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2315.81</v>
+        <v>2368.04</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>792.9</v>
+        <v>798.38</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>8438.860000000001</v>
+        <v>8497.120000000001</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>807.78</v>
+        <v>813.36</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>6917.9</v>
+        <v>6825.75</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>5137.84</v>
+        <v>5069.4</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1356.04</v>
+        <v>1337.97</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1072.45</v>
+        <v>1051.46</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3678.75</v>
+        <v>3606.74</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2525.14</v>
+        <v>2475.71</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>857.76</v>
+        <v>840.13</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3320.03</v>
+        <v>3251.8</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1308.05</v>
+        <v>1281.17</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1716.08</v>
+        <v>1680.81</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>28073</v>
+        <v>28339.67</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>4113.14</v>
+        <v>4152.21</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>10170.49</v>
+        <v>10272.78</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2427.91</v>
+        <v>2452.22</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>5163.31</v>
+        <v>5189.62</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>7494.52</v>
+        <v>7532.71</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>937.54</v>
+        <v>939.53</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>3587.75</v>
+        <v>3595.4</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1008.17</v>
+        <v>1014.74</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>4989.75</v>
+        <v>5022.28</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2949.2</v>
+        <v>2955.96</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>6175.61</v>
+        <v>6189.77</v>
       </c>
     </row>
     <row r="248">
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>3353.58</v>
+        <v>3376.03</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1057548-740-CM26</t>
+          <t>2284-569-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15601,17 +15601,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15621,12 +15621,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1055.82</v>
+        <v>7411.21</v>
       </c>
     </row>
     <row r="250">
@@ -15697,13 +15697,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5898.26</v>
+        <v>5939.54</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1057548-739-CM26</t>
+          <t>1057548-740-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15758,13 +15758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>898.3099999999999</v>
+        <v>1063.21</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2284-569-CM26</t>
+          <t>1057548-739-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15784,17 +15784,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15804,12 +15804,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>7359.7</v>
+        <v>904.6</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1453.63</v>
+        <v>1450.47</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3016</v>
+        <v>3009.44</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3812.27</v>
+        <v>3804.63</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>5207.89</v>
+        <v>5197.45</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>823.21</v>
+        <v>818.45</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1339.51</v>
+        <v>1331.76</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1668.11</v>
+        <v>1658.46</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1051.34</v>
+        <v>1045.25</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2781.24</v>
+        <v>2765.14</v>
       </c>
     </row>
     <row r="262">
@@ -16429,13 +16429,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>4240.98</v>
+        <v>4172.99</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1267885-679-CM26</t>
+          <t>2908-209-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16475,12 +16475,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16490,13 +16490,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>5387.74</v>
+        <v>1158.81</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1057547-11209-CM26</t>
+          <t>1267885-679-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16516,17 +16516,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16536,12 +16536,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
+          <t>76.592.530-4</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16551,13 +16551,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3602.94</v>
+        <v>5325.05</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2908-209-CM26</t>
+          <t>1057547-11209-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16577,17 +16577,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1172.45</v>
+        <v>3561.02</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,68 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>792.78</v>
+        <v>798.09</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2910-125-CM26</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>69.200.700-k</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>3711.24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
@@ -684,7 +684,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1375,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1440,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1566,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1692,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1818,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2192,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2566,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2631,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3009,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3074,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3200,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3265,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3330,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3395,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3460,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3525,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3590,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3716,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3842,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3907,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3972,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4098,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4468,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4659,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4785,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4850,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4976,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5293,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5358,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5423,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5549,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5679,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5988,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6053,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6118,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6244,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6370,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6435,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6561,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6687,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6813,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7000,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7374,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7500,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7565,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7630,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7695,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7821,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8142,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8268,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8333,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8398,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8585,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8837,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9211,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9276,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9341,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9715,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9780,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9845,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9910,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10036,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10288,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10540,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10605,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10853,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11410,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11662,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11727,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11914,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11979,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12044,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12170,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12235,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12792,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12979,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13044,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13109,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13235,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13300,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13365,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13430,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13495,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13560,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13686,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13873,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13938,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14003,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14068,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14255,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14320,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14446,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14511,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14576,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14641,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14706,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14771,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14836,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14901,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14966,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15092,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15157,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15222,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15287,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15352,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15417,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15482,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15547,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15612,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15677,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15742,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15807,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15872,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15937,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16002,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16067,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16193,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16258,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16323,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16449,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16514,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16701,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16766,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16831,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16896,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16961,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17026,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17091,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17156,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17343,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17408,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17473,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17660,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17851,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18282,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18408,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18473,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18538,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18725,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18790,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19164,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19534,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19660,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19851,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19916,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19981,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20046,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20111,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20176,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20363,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20428,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20493,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20558,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20623,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20688,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20753,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20818,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21066,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21192,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21257,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21383,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21509,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +21757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21883,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21948,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22013,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22078,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22326,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22391,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22456,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22582,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22647,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22712,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22777,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22903,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22968,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23033,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23159,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23224,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23350,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23541,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23606,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23732,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23797,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +23862,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23992,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24240,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24305,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24370,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24435,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +24622,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24874,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25061,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25126,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25191,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25256,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25321,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25386,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +25817,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +25882,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +25947,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26073,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26138,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26203,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26268,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26333,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26398,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26585,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26650,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +26776,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +26841,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27028,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27093,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27158,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27288,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27353,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27418,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27483,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27609,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +27674,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27739,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +27804,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +27869,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +27995,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28121,11 @@
           <t>77.983.294-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28186,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28251,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28316,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28442,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28507,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28572,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28698,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +28763,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +28828,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +28893,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29019,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29084,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29149,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29214,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29279,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29344,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29409,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29474,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29600,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29665,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29730,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +29795,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29860,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +29925,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +29990,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30177,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30303,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +30368,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30494,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30620,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +30746,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +30872,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31059,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31185,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31250,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31315,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31502,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31567,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31632,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31697,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +31762,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +31949,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32136,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32201,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32331,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +32518,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32583,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32709,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +32774,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +32839,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +32904,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +32969,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33034,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33099,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33164,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33229,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33294,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33420,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33485,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33550,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33676,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +33741,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
@@ -2696,7 +2696,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4163,7 +4167,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31380,7 +31388,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M525"/>
+  <dimension ref="A1:M560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17303,7 +17303,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5688-10-CM26</t>
+          <t>3140-4454-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17328,12 +17328,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.978.910-5</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17362,13 +17362,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>6971.94</v>
+        <v>3869.33</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3140-4454-CM26</t>
+          <t>1067355-60-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17393,12 +17393,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17427,13 +17427,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>3869.33</v>
+        <v>2135.94</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1067355-60-CM26</t>
+          <t>5688-10-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17458,12 +17458,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>61.978.910-5</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17492,7 +17492,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2135.94</v>
+        <v>6971.94</v>
       </c>
     </row>
     <row r="270">
@@ -17876,7 +17876,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1432083-98-CM26</t>
+          <t>1432083-79-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17916,28 +17916,32 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1337.34</v>
+        <v>6991.33</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1432083-97-CM26</t>
+          <t>1432083-78-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17977,28 +17981,32 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>912.55</v>
+        <v>5264.8</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1432083-96-CM26</t>
+          <t>1432083-80-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18038,28 +18046,32 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>838.8</v>
+        <v>14438.12</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1432083-94-CM26</t>
+          <t>1432083-91-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18114,13 +18126,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1017.66</v>
+        <v>955.86</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1432083-93-CM26</t>
+          <t>1432083-88-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18175,7 +18187,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>816.88</v>
+        <v>2054.41</v>
       </c>
     </row>
     <row r="281">
@@ -18242,7 +18254,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1432083-80-CM26</t>
+          <t>1432083-93-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18282,32 +18294,28 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>14438.12</v>
+        <v>816.88</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1432083-88-CM26</t>
+          <t>1432083-94-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18362,13 +18370,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2054.41</v>
+        <v>1017.66</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1432083-86-CM26</t>
+          <t>1432083-96-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18408,32 +18416,28 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2368.38</v>
+        <v>838.8</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1432083-79-CM26</t>
+          <t>1432083-97-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18473,32 +18477,28 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>6991.33</v>
+        <v>912.55</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1432083-78-CM26</t>
+          <t>1432083-98-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18538,32 +18538,28 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>5264.8</v>
+        <v>1337.34</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1432083-91-CM26</t>
+          <t>1432083-86-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18603,22 +18599,26 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>955.86</v>
+        <v>2368.38</v>
       </c>
     </row>
     <row r="288">
@@ -18998,7 +18998,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1432083-104-CM26</t>
+          <t>1432083-105-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19038,32 +19038,28 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>15295.33</v>
+        <v>895.3</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1432083-105-CM26</t>
+          <t>1432083-104-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19103,28 +19099,32 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>895.3</v>
+        <v>15295.33</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1426100-29-CM26</t>
+          <t>1432083-103-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19149,12 +19149,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19164,32 +19164,28 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>LOGISTRA SPA</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>78.209.481-5</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2999.18</v>
+        <v>814.1900000000001</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1432083-103-CM26</t>
+          <t>1426100-29-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19214,12 +19210,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19229,22 +19225,26 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>LOGISTRA SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr"/>
+          <t>78.209.481-5</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>814.1900000000001</v>
+        <v>2999.18</v>
       </c>
     </row>
     <row r="298">
@@ -19372,7 +19372,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1432083-121-CM26</t>
+          <t>1432083-118-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19427,13 +19427,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1426.15</v>
+        <v>1304.97</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1432083-120-CM26</t>
+          <t>1057545-150-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -19473,28 +19473,32 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr"/>
+          <t>77.745.829-9</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1968.43</v>
+        <v>4796.73</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1057545-150-CM26</t>
+          <t>1432083-116-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19519,12 +19523,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -19534,12 +19538,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>77.745.829-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -19553,13 +19557,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>4796.73</v>
+        <v>4491.87</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1432083-118-CM26</t>
+          <t>1432083-120-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19614,13 +19618,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1304.97</v>
+        <v>1968.43</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1432083-116-CM26</t>
+          <t>1432083-119-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19660,32 +19664,28 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>4491.87</v>
+        <v>834.84</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1432083-119-CM26</t>
+          <t>1432083-121-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19740,7 +19740,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>834.84</v>
+        <v>1426.15</v>
       </c>
     </row>
     <row r="306">
@@ -20136,7 +20136,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>707424-13-CM26</t>
+          <t>5538-25-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20161,12 +20161,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20176,17 +20176,17 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>31904.54</v>
+        <v>15253.64</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3850-53-CM26</t>
+          <t>5538-26-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20221,17 +20221,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20241,28 +20241,32 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1788.91</v>
+        <v>3512.26</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1057547-3379-CM26</t>
+          <t>2284-188-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20282,17 +20286,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20302,22 +20306,26 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1660.06</v>
+        <v>7345.46</v>
       </c>
     </row>
     <row r="315">
@@ -20388,7 +20396,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5538-25-CM26</t>
+          <t>707424-13-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20413,12 +20421,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20428,17 +20436,17 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -20447,13 +20455,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>15253.64</v>
+        <v>31904.54</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5538-27-CM26</t>
+          <t>3850-53-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20473,17 +20481,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20493,32 +20501,28 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.287.477-6</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3305.48</v>
+        <v>1788.91</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5538-26-CM26</t>
+          <t>1057547-3379-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20543,12 +20547,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20558,26 +20562,22 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>3512.26</v>
+        <v>1660.06</v>
       </c>
     </row>
     <row r="319">
@@ -20648,7 +20648,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2284-188-CM26</t>
+          <t>5538-27-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20668,17 +20668,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20688,17 +20688,17 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -20707,13 +20707,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>7345.46</v>
+        <v>3305.48</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>5538-29-CM26</t>
+          <t>1057547-3457-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20738,12 +20738,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20753,32 +20753,28 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2284.19</v>
+        <v>6436.38</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5538-30-CM26</t>
+          <t>5538-29-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20818,12 +20814,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -20837,13 +20833,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>5846.47</v>
+        <v>2284.19</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5538-31-CM26</t>
+          <t>5538-30-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20883,28 +20879,32 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>20227.46</v>
+        <v>5846.47</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5538-32-CM26</t>
+          <t>5538-31-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20959,13 +20959,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>5073.52</v>
+        <v>20227.46</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1057547-3457-CM26</t>
+          <t>5538-32-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20990,12 +20990,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21005,12 +21005,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -21020,7 +21020,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>6436.38</v>
+        <v>5073.52</v>
       </c>
     </row>
     <row r="326">
@@ -21091,7 +21091,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1057550-76-CM26</t>
+          <t>1432083-157-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21116,12 +21116,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.607.505-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21131,12 +21131,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.132.256-7</t>
         </is>
       </c>
       <c r="K327" t="inlineStr"/>
@@ -21146,13 +21146,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>3875.66</v>
+        <v>2468.26</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5612-30-CM26</t>
+          <t>2910-32-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21177,12 +21177,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21192,32 +21192,28 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>3755.93</v>
+        <v>2712.02</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5538-54-CM26</t>
+          <t>2910-33-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21242,12 +21238,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21276,13 +21272,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3173.81</v>
+        <v>8879.709999999999</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1057547-3668-CM26</t>
+          <t>1189881-4-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21307,12 +21303,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21322,12 +21318,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="K330" t="inlineStr"/>
@@ -21337,7 +21333,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>5929.6</v>
+        <v>1551.76</v>
       </c>
     </row>
     <row r="331">
@@ -21408,7 +21404,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1432083-157-CM26</t>
+          <t>1057550-76-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21433,12 +21429,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.505-5</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -21448,12 +21444,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -21463,13 +21459,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2468.26</v>
+        <v>3875.66</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2910-33-CM26</t>
+          <t>1057547-3668-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21494,12 +21490,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21509,32 +21505,28 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>8879.709999999999</v>
+        <v>5929.6</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2910-32-CM26</t>
+          <t>5538-54-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21559,12 +21551,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21574,28 +21566,32 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2712.02</v>
+        <v>3173.81</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1189881-4-CM26</t>
+          <t>5612-30-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21620,12 +21616,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -21635,22 +21631,26 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1551.76</v>
+        <v>3755.93</v>
       </c>
     </row>
     <row r="336">
@@ -21908,7 +21908,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1057553-95-CM26</t>
+          <t>3335-165-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21928,17 +21928,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21948,17 +21948,17 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -21967,7 +21967,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>5951.05</v>
+        <v>1035.72</v>
       </c>
     </row>
     <row r="341">
@@ -22038,7 +22038,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>3335-165-CM26</t>
+          <t>1057553-95-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22058,17 +22058,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22078,17 +22078,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -22097,7 +22097,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>1035.72</v>
+        <v>5951.05</v>
       </c>
     </row>
     <row r="343">
@@ -22164,7 +22164,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1432083-401-CM26</t>
+          <t>1057547-3880-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22184,17 +22184,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22204,12 +22204,12 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -22219,13 +22219,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>7200.88</v>
+        <v>1168.02</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1057547-3880-CM26</t>
+          <t>1432083-401-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22245,17 +22245,17 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22265,12 +22265,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
+          <t>76.132.256-7</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -22280,7 +22280,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1168.02</v>
+        <v>7200.88</v>
       </c>
     </row>
     <row r="346">
@@ -22351,7 +22351,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1057552-196-CM26</t>
+          <t>1426100-48-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22376,12 +22376,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22391,32 +22391,28 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2436.57</v>
+        <v>1537.66</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1067355-114-CM26</t>
+          <t>1426100-49-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22441,12 +22437,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22475,13 +22471,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>7150.04</v>
+        <v>2705.47</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1426100-48-CM26</t>
+          <t>1067355-114-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22506,12 +22502,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22521,28 +22517,32 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K349" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1537.66</v>
+        <v>7150.04</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1426100-49-CM26</t>
+          <t>1057552-196-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22567,12 +22567,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22582,17 +22582,17 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -22601,7 +22601,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2705.47</v>
+        <v>2436.57</v>
       </c>
     </row>
     <row r="351">
@@ -23058,7 +23058,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5538-79-CM26</t>
+          <t>1057549-146-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23083,12 +23083,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23098,28 +23098,32 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2969.74</v>
+        <v>1278.35</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1057549-146-CM26</t>
+          <t>1057550-106-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23144,12 +23148,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>61.607.505-5</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23159,17 +23163,17 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -23178,13 +23182,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1278.35</v>
+        <v>7359.02</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1057550-106-CM26</t>
+          <t>5538-80-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23209,12 +23213,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.607.505-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23224,32 +23228,28 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K360" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.189.387-2</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>7359.02</v>
+        <v>2408.79</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5538-80-CM26</t>
+          <t>5538-79-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23304,13 +23304,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2408.79</v>
+        <v>2969.74</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>3986-121-CM26</t>
+          <t>1432083-574-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23330,17 +23330,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23350,32 +23350,28 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2209.27</v>
+        <v>2010.2</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1432083-574-CM26</t>
+          <t>3986-121-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23395,17 +23391,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23415,22 +23411,26 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K363" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2010.2</v>
+        <v>2209.27</v>
       </c>
     </row>
     <row r="364">
@@ -24460,7 +24460,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1035685-121-CM26</t>
+          <t>707424-25-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -24480,17 +24480,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -24500,28 +24500,32 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K380" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>799.62</v>
+        <v>35229.01</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1057547-5949-CM26</t>
+          <t>1035685-121-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24546,12 +24550,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24561,12 +24565,12 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K381" t="inlineStr"/>
@@ -24576,13 +24580,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>5671.37</v>
+        <v>799.62</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>707424-25-CM26</t>
+          <t>1057547-5949-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -24602,17 +24606,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -24622,26 +24626,22 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K382" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>35229.01</v>
+        <v>5671.37</v>
       </c>
     </row>
     <row r="383">
@@ -25216,7 +25216,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2284-365-CM26</t>
+          <t>1057547-6604-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25236,17 +25236,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25256,26 +25256,22 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K392" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>7705.74</v>
+        <v>1062.56</v>
       </c>
     </row>
     <row r="393">
@@ -25346,7 +25342,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1497-69-CM26</t>
+          <t>2284-365-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25366,17 +25362,17 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -25386,17 +25382,17 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -25405,13 +25401,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>4047.61</v>
+        <v>7705.74</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1057547-6604-CM26</t>
+          <t>1497-69-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25436,12 +25432,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25451,22 +25447,26 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K395" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>1062.56</v>
+        <v>4047.61</v>
       </c>
     </row>
     <row r="396">
@@ -26163,7 +26163,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1057548-533-CM26</t>
+          <t>1057548-534-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26203,12 +26203,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PAPELES AUSTRAL SPA</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.404.653-4</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
@@ -26222,13 +26222,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2994.31</v>
+        <v>3988.91</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1057548-534-CM26</t>
+          <t>1057548-536-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26268,17 +26268,17 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>PAPELES AUSTRAL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>77.404.653-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -26287,13 +26287,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3988.91</v>
+        <v>4006.84</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1057548-536-CM26</t>
+          <t>1057548-533-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26333,17 +26333,17 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -26352,13 +26352,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>4006.84</v>
+        <v>2994.31</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>511077-49-CM26</t>
+          <t>1057547-7516-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26383,12 +26383,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26398,32 +26398,28 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1292.14</v>
+        <v>2314.18</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1057547-7516-CM26</t>
+          <t>511077-49-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26448,12 +26444,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -26463,22 +26459,26 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K411" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2314.18</v>
+        <v>1292.14</v>
       </c>
     </row>
     <row r="412">
@@ -27378,7 +27378,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1057549-281-CM26</t>
+          <t>1422032-60-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -27398,17 +27398,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>65.035.343-9</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -27418,17 +27418,17 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -27437,13 +27437,13 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>798.38</v>
+        <v>813.36</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>1422032-60-CM26</t>
+          <t>1057549-281-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -27463,17 +27463,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>65.035.343-9</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -27483,17 +27483,17 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -27502,13 +27502,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>813.36</v>
+        <v>798.38</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>1057547-9370-CM26</t>
+          <t>1057553-226-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -27533,12 +27533,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -27548,28 +27548,32 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>6825.75</v>
+        <v>5069.4</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1057553-226-CM26</t>
+          <t>1035685-201-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -27589,17 +27593,17 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -27628,13 +27632,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>5069.4</v>
+        <v>1337.97</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1035685-201-CM26</t>
+          <t>1057547-9370-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -27654,17 +27658,17 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -27674,26 +27678,22 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K430" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>1337.97</v>
+        <v>6825.75</v>
       </c>
     </row>
     <row r="431">
@@ -28402,7 +28402,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>630424-438-CM26</t>
+          <t>1057548-709-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -28427,12 +28427,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28442,17 +28442,17 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -28461,13 +28461,13 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>7532.71</v>
+        <v>5189.62</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1057548-709-CM26</t>
+          <t>630424-438-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -28492,12 +28492,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -28507,17 +28507,17 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -28526,7 +28526,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>5189.62</v>
+        <v>7532.71</v>
       </c>
     </row>
     <row r="444">
@@ -29044,7 +29044,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1057548-739-CM26</t>
+          <t>1057548-740-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29084,17 +29084,17 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -29103,13 +29103,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>904.6</v>
+        <v>1063.21</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1057548-740-CM26</t>
+          <t>1057548-739-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29149,17 +29149,17 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -29168,13 +29168,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>1063.21</v>
+        <v>904.6</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2284-569-CM26</t>
+          <t>3568-489-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29199,12 +29199,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29214,12 +29214,12 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
@@ -29233,13 +29233,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>7411.21</v>
+        <v>5939.54</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>3568-489-CM26</t>
+          <t>2284-569-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29264,12 +29264,12 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -29279,12 +29279,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
@@ -29298,13 +29298,13 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>5939.54</v>
+        <v>7411.21</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>926853-48-CM26</t>
+          <t>1057552-642-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -29324,17 +29324,17 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -29344,12 +29344,12 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
@@ -29363,13 +29363,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1450.47</v>
+        <v>3009.44</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1057552-642-CM26</t>
+          <t>926853-48-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -29389,17 +29389,17 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -29409,12 +29409,12 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
@@ -29428,13 +29428,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>3009.44</v>
+        <v>1450.47</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1057547-10869-CM26</t>
+          <t>3334-325-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -29454,17 +29454,17 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -29474,32 +29474,28 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>prodesa</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K458" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.828.760-5</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>5197.45</v>
+        <v>3804.63</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>3334-325-CM26</t>
+          <t>1057547-10869-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -29519,17 +29515,17 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -29539,22 +29535,26 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>prodesa</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>96.828.760-5</t>
-        </is>
-      </c>
-      <c r="K459" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>3804.63</v>
+        <v>5197.45</v>
       </c>
     </row>
     <row r="460">
@@ -30771,7 +30771,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2910-128-CM26</t>
+          <t>299-146-CM26</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -30796,12 +30796,12 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -30826,13 +30826,13 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>2304.08</v>
+        <v>807.59</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>299-144-CM26</t>
+          <t>1057547-12306-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -30852,17 +30852,17 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -30872,32 +30872,28 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>RED OFFICE SUR LTDA.</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>77.806.000-0</t>
-        </is>
-      </c>
-      <c r="K480" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>823.23</v>
+        <v>3455.18</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>299-146-CM26</t>
+          <t>2910-128-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -30922,12 +30918,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -30952,13 +30948,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>807.59</v>
+        <v>2304.08</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1057547-12306-CM26</t>
+          <t>299-144-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -30978,17 +30974,17 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -30998,22 +30994,26 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
-        </is>
-      </c>
-      <c r="K482" t="inlineStr"/>
+          <t>77.806.000-0</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>3455.18</v>
+        <v>823.23</v>
       </c>
     </row>
     <row r="483">
@@ -31340,7 +31340,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2986-359-CM26</t>
+          <t>4062-592-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -31365,12 +31365,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -31380,32 +31380,28 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K488" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>934.8</v>
+        <v>823.87</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>4062-592-CM26</t>
+          <t>2986-359-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -31430,12 +31426,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -31445,22 +31441,26 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K489" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>823.87</v>
+        <v>934.8</v>
       </c>
     </row>
     <row r="490">
@@ -31913,7 +31913,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>3335-1161-CM26</t>
+          <t>5418-195-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -31938,12 +31938,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.978.900-8</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -31953,17 +31953,17 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -31972,13 +31972,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>1043</v>
+        <v>6198.87</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>1057547-13576-CM26</t>
+          <t>1057545-1015-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32003,12 +32003,12 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.500-4</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD LOS RIOS</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -32018,28 +32018,32 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K498" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>3395.96</v>
+        <v>2117.95</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>1057547-13575-CM26</t>
+          <t>1057547-13571-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32059,7 +32063,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -32079,28 +32083,32 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Barron Vieyra International Ltda.</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>78.723.570-0</t>
-        </is>
-      </c>
-      <c r="K499" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>1951.84</v>
+        <v>6599</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>3140-4854-CM26</t>
+          <t>1057547-13572-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32125,12 +32133,12 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -32140,32 +32148,28 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K500" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>2559.3</v>
+        <v>37948.1</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1057547-13571-CM26</t>
+          <t>1057547-13575-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32205,32 +32209,28 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>Barron Vieyra International Ltda.</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
-        </is>
-      </c>
-      <c r="K501" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.723.570-0</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>6599</v>
+        <v>1951.84</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1057545-1015-CM26</t>
+          <t>1057547-13576-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -32255,12 +32255,12 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>61.607.500-4</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -32270,32 +32270,28 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K502" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2117.95</v>
+        <v>3395.96</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>5418-195-CM26</t>
+          <t>3140-4854-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -32315,17 +32311,17 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>61.978.900-8</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LOS RIOS</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -32354,13 +32350,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>6198.87</v>
+        <v>2559.3</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1057547-13572-CM26</t>
+          <t>3335-1161-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -32380,17 +32376,17 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -32400,28 +32396,32 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K504" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>37948.1</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>1057547-13658-CM26</t>
+          <t>3986-310-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -32441,17 +32441,17 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -32461,28 +32461,32 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K505" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2194.41</v>
+        <v>2222.9</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>5538-261-CM26</t>
+          <t>1057547-13658-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -32507,12 +32511,12 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -32522,32 +32526,28 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K506" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>4097.28</v>
+        <v>2194.41</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>3986-310-CM26</t>
+          <t>3545-235-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -32567,17 +32567,17 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>65.273.020-5</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -32587,17 +32587,17 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -32606,7 +32606,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2222.9</v>
+        <v>2282.08</v>
       </c>
     </row>
     <row r="508">
@@ -32738,7 +32738,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>3545-235-CM26</t>
+          <t>5538-261-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>65.273.020-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -32778,17 +32778,17 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -32797,7 +32797,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2282.08</v>
+        <v>4097.28</v>
       </c>
     </row>
     <row r="511">
@@ -33148,7 +33148,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -33213,7 +33213,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -33384,7 +33384,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>3334-460-CM26</t>
+          <t>1057552-918-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -33404,17 +33404,17 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -33424,17 +33424,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -33443,13 +33443,13 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>16598.02</v>
+        <v>2661.39</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>1057552-918-CM26</t>
+          <t>3334-460-CM26</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -33469,17 +33469,17 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -33489,17 +33489,17 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -33508,13 +33508,13 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2661.39</v>
+        <v>16598.02</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>4062-694-CM26</t>
+          <t>2284-745-CM26</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -33529,7 +33529,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -33539,12 +33539,12 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -33554,12 +33554,12 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>RED OFFICE SUR LTDA.</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.806.000-0</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
@@ -33573,13 +33573,13 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2067.72</v>
+        <v>7398.85</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1432083-2382-CM26</t>
+          <t>4062-694-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -33594,22 +33594,22 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -33619,22 +33619,26 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K523" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>1015.88</v>
+        <v>2067.72</v>
       </c>
     </row>
     <row r="524">
@@ -33660,7 +33664,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -33705,66 +33709,2301 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
+          <t>1432083-2382-CM26</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>61.981.110-0</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA VYB</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M525" s="2" t="n">
+        <v>1015.88</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
           <t>3568-663-CM26</t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B526" t="inlineStr">
         <is>
           <t>2239-8-LR25</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
+      <c r="C526" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr">
+      <c r="D526" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E525" t="inlineStr">
+      <c r="E526" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr">
+      <c r="F526" t="inlineStr">
         <is>
           <t>69.201.200-3</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr">
+      <c r="G526" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
-      <c r="I525" t="inlineStr">
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
         </is>
       </c>
-      <c r="J525" t="inlineStr">
+      <c r="J526" t="inlineStr">
         <is>
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr">
+      <c r="K526" t="inlineStr">
         <is>
           <t>Antofagasta</t>
         </is>
       </c>
-      <c r="L525" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M525" s="2" t="n">
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M526" s="2" t="n">
         <v>1164.75</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>3850-502-CM26</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>69.201.000-0</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M527" s="2" t="n">
+        <v>2723.17</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>1057553-357-CM26</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>61.607.509-8</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M528" s="2" t="n">
+        <v>2319.26</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>5751-260-CM26</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>61.818.002-6</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M529" s="2" t="n">
+        <v>3587.64</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>1426100-202-CM26</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M530" s="2" t="n">
+        <v>2718.23</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>1426100-203-CM26</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M531" s="2" t="n">
+        <v>1381.28</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2908-270-CM26</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M532" s="2" t="n">
+        <v>1011.2</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2908-271-CM26</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>69.200.300-4</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LANCO</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M533" s="2" t="n">
+        <v>4883.62</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>1057553-360-CM26</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>61.607.509-8</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M534" s="2" t="n">
+        <v>1747.42</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>5657-288-CM26</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>PROVEEDORA KENUA SPA</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>78.212.867-1</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M535" s="2" t="n">
+        <v>883.9</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>1057548-1076-CM26</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>61.607.503-9</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M536" s="2" t="n">
+        <v>1851.76</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>5612-196-CM26</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M537" s="2" t="n">
+        <v>6446.19</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>3335-1386-CM26</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>69.200.800-6</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M538" s="2" t="n">
+        <v>838.74</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>1218393-453-CM26</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>53.335.808-K</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M539" s="2" t="n">
+        <v>4355.58</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>5538-305-CM26</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M540" s="2" t="n">
+        <v>9626.91</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>1057548-1100-CM26</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>61.607.503-9</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M541" s="2" t="n">
+        <v>1512.36</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>3789-595-CM26</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>69.200.900-2</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>MONARQUÍA SPA</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>78.199.695-5</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M542" s="2" t="n">
+        <v>4270.22</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>3789-594-CM26</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>69.200.900-2</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M543" s="2" t="n">
+        <v>3509.83</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>1067355-494-CM26</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>61.980.670-0</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M544" s="2" t="n">
+        <v>9434.68</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2986-480-CM26</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>69.200.600-3</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M545" s="2" t="n">
+        <v>5428.68</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>1218393-458-CM26</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>53.335.808-K</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Equilibrium SpA</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M546" s="2" t="n">
+        <v>2165.35</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>1057547-15255-CM26</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M547" s="2" t="n">
+        <v>5455.27</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>1057547-15275-CM26</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>MARYUN Seguridad Industrial</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M548" s="2" t="n">
+        <v>1676.02</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>1057547-15361-CM26</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M549" s="2" t="n">
+        <v>1588.53</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>1057547-15358-CM26</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M550" s="2" t="n">
+        <v>5373.95</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>1057547-15359-CM26</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>MARYUN Seguridad Industrial</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M551" s="2" t="n">
+        <v>2540.99</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>1057552-1003-CM26</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>61.607.508-K</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M552" s="2" t="n">
+        <v>3313.24</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>1057547-15332-CM26</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>MARYUN Seguridad Industrial</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M553" s="2" t="n">
+        <v>6337.01</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>1067355-503-CM26</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>61.980.670-0</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M554" s="2" t="n">
+        <v>933.9</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>1057548-1147-CM26</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>61.607.503-9</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M555" s="2" t="n">
+        <v>2511.1</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>1057547-15378-CM26</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M556" s="2" t="n">
+        <v>3535.81</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>5740-389-CM26</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>61.979.060-k</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M557" s="2" t="n">
+        <v>1686.08</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>5538-310-CM26</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M558" s="2" t="n">
+        <v>1432.87</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>5538-312-CM26</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M559" s="2" t="n">
+        <v>1143.58</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>1057547-15455-CM26</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>61.607.502-0</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>MARYUN Seguridad Industrial</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M560" s="2" t="n">
+        <v>942.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/los-rios.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M566"/>
+  <dimension ref="A1:M569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17490,7 +17490,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3140-4454-CM26</t>
+          <t>5688-10-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17515,12 +17515,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.978.910-5</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17549,13 +17549,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>3869.33</v>
+        <v>6971.94</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1067355-60-CM26</t>
+          <t>3140-4454-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17580,12 +17580,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17614,13 +17614,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2135.94</v>
+        <v>3869.33</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5688-10-CM26</t>
+          <t>1067355-60-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17645,12 +17645,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.978.910-5</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17679,7 +17679,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>6971.94</v>
+        <v>2135.94</v>
       </c>
     </row>
     <row r="273">
@@ -17872,7 +17872,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1432083-85-CM26</t>
+          <t>1432083-87-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17912,28 +17912,32 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2361.22</v>
+        <v>2477.48</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1432083-87-CM26</t>
+          <t>1432083-90-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17992,13 +17996,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2477.48</v>
+        <v>3038.34</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1432083-90-CM26</t>
+          <t>1432083-85-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18038,32 +18042,28 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>3038.34</v>
+        <v>2361.22</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1432083-79-CM26</t>
+          <t>1432083-97-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18103,26 +18103,22 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>6991.33</v>
+        <v>912.55</v>
       </c>
     </row>
     <row r="280">
@@ -18193,7 +18189,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1432083-80-CM26</t>
+          <t>1432083-98-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18233,32 +18229,28 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>14438.12</v>
+        <v>1337.34</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1432083-91-CM26</t>
+          <t>1432083-79-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18298,28 +18290,32 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>955.86</v>
+        <v>6991.33</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1432083-88-CM26</t>
+          <t>1432083-80-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18359,28 +18355,32 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2054.41</v>
+        <v>14438.12</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1432083-92-CM26</t>
+          <t>1432083-86-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18420,28 +18420,32 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1778.2</v>
+        <v>2368.38</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1432083-93-CM26</t>
+          <t>1432083-88-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18496,13 +18500,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>816.88</v>
+        <v>2054.41</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1432083-94-CM26</t>
+          <t>1432083-91-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18557,13 +18561,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1017.66</v>
+        <v>955.86</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1432083-96-CM26</t>
+          <t>1432083-92-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18618,13 +18622,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>838.8</v>
+        <v>1778.2</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1432083-97-CM26</t>
+          <t>1432083-96-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18679,13 +18683,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>912.55</v>
+        <v>838.8</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1432083-98-CM26</t>
+          <t>1432083-93-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18740,13 +18744,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1337.34</v>
+        <v>816.88</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1432083-86-CM26</t>
+          <t>1432083-94-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18786,32 +18790,28 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2368.38</v>
+        <v>1017.66</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1057547-2565-CM26</t>
+          <t>1057552-109-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18836,12 +18836,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18851,28 +18851,32 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1794.59</v>
+        <v>3336.51</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1057552-109-CM26</t>
+          <t>1057547-2565-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18897,12 +18901,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18912,32 +18916,28 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3336.51</v>
+        <v>1794.59</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1218393-45-CM26</t>
+          <t>1057547-2631-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18962,12 +18962,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>53.335.808-K</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18977,32 +18977,28 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1531.08</v>
+        <v>2485.86</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1057547-2631-CM26</t>
+          <t>1218393-45-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19027,12 +19023,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>53.335.808-K</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19042,28 +19038,32 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2485.86</v>
+        <v>1531.08</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1432083-106-CM26</t>
+          <t>1432083-105-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19118,7 +19118,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1933.16</v>
+        <v>895.3</v>
       </c>
     </row>
     <row r="296">
@@ -19185,7 +19185,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1432083-105-CM26</t>
+          <t>1432083-106-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19240,7 +19240,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>895.3</v>
+        <v>1933.16</v>
       </c>
     </row>
     <row r="298">
@@ -19559,7 +19559,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1432083-118-CM26</t>
+          <t>1432083-119-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19614,7 +19614,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1304.97</v>
+        <v>834.84</v>
       </c>
     </row>
     <row r="304">
@@ -19685,7 +19685,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1432083-116-CM26</t>
+          <t>1432083-118-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19725,26 +19725,22 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>4491.87</v>
+        <v>1304.97</v>
       </c>
     </row>
     <row r="306">
@@ -19811,7 +19807,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1432083-119-CM26</t>
+          <t>1432083-116-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19851,22 +19847,26 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>834.84</v>
+        <v>4491.87</v>
       </c>
     </row>
     <row r="308">
@@ -20063,7 +20063,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1432083-145-CM26</t>
+          <t>1432083-159-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20083,7 +20083,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -20122,13 +20122,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>810.28</v>
+        <v>2357.74</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1432083-159-CM26</t>
+          <t>1432083-145-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20148,7 +20148,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -20187,7 +20187,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2357.74</v>
+        <v>810.28</v>
       </c>
     </row>
     <row r="313">
@@ -20323,7 +20323,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5538-25-CM26</t>
+          <t>2905-133-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20348,12 +20348,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20363,17 +20363,17 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -20382,13 +20382,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>15253.64</v>
+        <v>6610.2</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5538-26-CM26</t>
+          <t>5538-25-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20447,13 +20447,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3512.26</v>
+        <v>15253.64</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2284-188-CM26</t>
+          <t>5538-27-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20473,17 +20473,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20493,17 +20493,17 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -20512,13 +20512,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>7345.46</v>
+        <v>3305.48</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5538-28-CM26</t>
+          <t>2284-188-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20538,17 +20538,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20558,12 +20558,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -20577,13 +20577,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>7225.18</v>
+        <v>7345.46</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>707424-13-CM26</t>
+          <t>5538-28-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20608,12 +20608,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -20623,12 +20623,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -20642,13 +20642,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>31904.54</v>
+        <v>7225.18</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>3850-53-CM26</t>
+          <t>707424-13-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20668,17 +20668,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -20688,28 +20688,32 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1788.91</v>
+        <v>31904.54</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1057547-3379-CM26</t>
+          <t>3850-53-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20729,17 +20733,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20749,12 +20753,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
+          <t>76.287.477-6</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -20764,13 +20768,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1660.06</v>
+        <v>1788.91</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2905-133-CM26</t>
+          <t>1057547-3379-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20795,12 +20799,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20810,32 +20814,28 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>6610.2</v>
+        <v>1660.06</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5538-27-CM26</t>
+          <t>5538-26-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20894,13 +20894,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3305.48</v>
+        <v>3512.26</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1057547-3457-CM26</t>
+          <t>5538-29-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20925,12 +20925,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20940,28 +20940,32 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr"/>
+          <t>77.621.112-5</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>6436.38</v>
+        <v>2284.19</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5538-29-CM26</t>
+          <t>5538-31-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21001,32 +21005,28 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.189.387-2</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2284.19</v>
+        <v>20227.46</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5538-30-CM26</t>
+          <t>5538-32-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21066,32 +21066,28 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.189.387-2</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>5846.47</v>
+        <v>5073.52</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5538-31-CM26</t>
+          <t>1057547-3457-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21116,12 +21112,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21131,12 +21127,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K327" t="inlineStr"/>
@@ -21146,13 +21142,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>20227.46</v>
+        <v>6436.38</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5538-32-CM26</t>
+          <t>5538-30-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21192,22 +21188,26 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>5073.52</v>
+        <v>5846.47</v>
       </c>
     </row>
     <row r="329">
@@ -21278,7 +21278,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1432083-157-CM26</t>
+          <t>1432083-151-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21333,13 +21333,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2468.26</v>
+        <v>1027.62</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5538-54-CM26</t>
+          <t>1432083-157-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21364,12 +21364,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21379,32 +21379,28 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.132.256-7</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>3173.81</v>
+        <v>2468.26</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1057547-3668-CM26</t>
+          <t>2910-32-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21429,12 +21425,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -21444,12 +21440,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -21459,13 +21455,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>5929.6</v>
+        <v>2712.02</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1057550-76-CM26</t>
+          <t>2910-33-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21490,12 +21486,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.607.505-5</t>
+          <t>69.200.700-k</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21505,28 +21501,32 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>3875.66</v>
+        <v>8879.709999999999</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5612-30-CM26</t>
+          <t>1189881-4-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21551,12 +21551,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21566,32 +21566,28 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.189.387-2</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>3755.93</v>
+        <v>1551.76</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1189881-4-CM26</t>
+          <t>5538-52-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21616,12 +21612,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -21631,28 +21627,32 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1551.76</v>
+        <v>4601.07</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2910-33-CM26</t>
+          <t>1057550-76-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -21677,12 +21677,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.607.505-5</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21692,32 +21692,28 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>8879.709999999999</v>
+        <v>3875.66</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2910-32-CM26</t>
+          <t>1057547-3668-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21742,12 +21738,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.200.700-k</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FUTRONO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21757,12 +21753,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K337" t="inlineStr"/>
@@ -21772,13 +21768,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2712.02</v>
+        <v>5929.6</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5538-52-CM26</t>
+          <t>5538-54-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21837,13 +21833,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>4601.07</v>
+        <v>3173.81</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1432083-151-CM26</t>
+          <t>5612-30-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21868,12 +21864,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21883,28 +21879,32 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>COMERCIAL Y DISTRIBUIDORA CENTELLA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>76.132.256-7</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>1027.62</v>
+        <v>3755.93</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1057550-80-CM26</t>
+          <t>4062-161-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21929,12 +21929,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.607.505-5</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21944,17 +21944,17 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -21963,13 +21963,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>12269.2</v>
+        <v>3108.93</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1057547-3743-CM26</t>
+          <t>1057550-80-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21994,12 +21994,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.505-5</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22009,28 +22009,32 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>11110.96</v>
+        <v>12269.2</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>4062-161-CM26</t>
+          <t>1057547-3743-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22055,12 +22059,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22070,26 +22074,22 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>3108.93</v>
+        <v>11110.96</v>
       </c>
     </row>
     <row r="343">
@@ -22355,7 +22355,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1057547-3880-CM26</t>
+          <t>952946-34-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22375,17 +22375,17 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22395,12 +22395,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>Distribuidora Surmontt</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
+          <t>76.287.477-6</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -22410,7 +22410,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1168.02</v>
+        <v>1437.42</v>
       </c>
     </row>
     <row r="348">
@@ -22477,7 +22477,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>952946-34-CM26</t>
+          <t>1057547-3880-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22497,17 +22497,17 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22517,12 +22517,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>Distribuidora Surmontt</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>76.287.477-6</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K349" t="inlineStr"/>
@@ -22532,7 +22532,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1437.42</v>
+        <v>1168.02</v>
       </c>
     </row>
     <row r="350">
@@ -23245,7 +23245,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1057549-146-CM26</t>
+          <t>1057550-106-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23270,12 +23270,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.607.504-7</t>
+          <t>61.607.505-5</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23285,17 +23285,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -23304,13 +23304,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1278.35</v>
+        <v>7359.02</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1057550-106-CM26</t>
+          <t>5538-79-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23335,12 +23335,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.607.505-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE C</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23350,32 +23350,28 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>77.189.387-2</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K362" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.189.387-2</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>7359.02</v>
+        <v>2969.74</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>5538-79-CM26</t>
+          <t>5538-80-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23430,13 +23426,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2969.74</v>
+        <v>2408.79</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5538-80-CM26</t>
+          <t>1057549-146-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23461,12 +23457,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.504-7</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LANC</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -23476,22 +23472,26 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>77.189.387-2</t>
-        </is>
-      </c>
-      <c r="K364" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2408.79</v>
+        <v>1278.35</v>
       </c>
     </row>
     <row r="365">
@@ -24517,7 +24517,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>952946-72-CM26</t>
+          <t>2905-274-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24542,12 +24542,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24557,17 +24557,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -24576,13 +24576,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1220.39</v>
+        <v>4195.64</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2905-274-CM26</t>
+          <t>952946-72-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -24607,12 +24607,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -24622,17 +24622,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -24641,7 +24641,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>4195.64</v>
+        <v>1220.39</v>
       </c>
     </row>
     <row r="383">
@@ -24773,7 +24773,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1035685-121-CM26</t>
+          <t>707424-25-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -24793,17 +24793,17 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -24813,28 +24813,32 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K385" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>799.62</v>
+        <v>35229.01</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>707424-25-CM26</t>
+          <t>1035685-121-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -24854,17 +24858,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24874,32 +24878,28 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K386" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>35229.01</v>
+        <v>799.62</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>4777-354-CM26</t>
+          <t>952946-74-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24919,17 +24919,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24939,28 +24939,32 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1469.32</v>
+        <v>805.96</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>952946-74-CM26</t>
+          <t>4777-354-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24980,17 +24984,17 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25000,26 +25004,22 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K388" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>805.96</v>
+        <v>1469.32</v>
       </c>
     </row>
     <row r="389">
@@ -25468,7 +25468,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1057547-6604-CM26</t>
+          <t>1497-69-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25493,12 +25493,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -25508,28 +25508,32 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K396" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1062.56</v>
+        <v>4047.61</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1057547-6611-CM26</t>
+          <t>1057547-6604-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25569,32 +25573,28 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1272.96</v>
+        <v>1062.56</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2284-365-CM26</t>
+          <t>1057547-6611-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -25614,17 +25614,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -25653,13 +25653,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>7705.74</v>
+        <v>1272.96</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1497-69-CM26</t>
+          <t>2284-365-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -25679,17 +25679,17 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -25699,17 +25699,17 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
@@ -25718,13 +25718,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>4047.61</v>
+        <v>7705.74</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1057547-6707-CM26</t>
+          <t>1057547-6732-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -25764,12 +25764,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K400" t="inlineStr"/>
@@ -25779,13 +25779,13 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2395.3</v>
+        <v>3287.15</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1057547-6732-CM26</t>
+          <t>1057547-6707-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -25825,12 +25825,12 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
+          <t>77.084.730-3</t>
         </is>
       </c>
       <c r="K401" t="inlineStr"/>
@@ -25840,13 +25840,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>3287.15</v>
+        <v>2395.3</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1057547-6858-CM26</t>
+          <t>3789-248-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -25866,17 +25866,17 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -25886,28 +25886,32 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>MONARQUÍA SPA</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr"/>
+          <t>78.199.695-5</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>3756.33</v>
+        <v>3848.97</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1057547-6861-CM26</t>
+          <t>1057547-6858-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -25947,12 +25951,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
+          <t>78.809.560-0</t>
         </is>
       </c>
       <c r="K403" t="inlineStr"/>
@@ -25962,7 +25966,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2542.7</v>
+        <v>3756.33</v>
       </c>
     </row>
     <row r="404">
@@ -26029,7 +26033,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>3789-248-CM26</t>
+          <t>1057547-6861-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26049,17 +26053,17 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26069,26 +26073,22 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>MONARQUÍA SPA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>78.199.695-5</t>
-        </is>
-      </c>
-      <c r="K405" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>3848.97</v>
+        <v>2542.7</v>
       </c>
     </row>
     <row r="406">
@@ -26159,7 +26159,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1426100-77-CM26</t>
+          <t>3850-222-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26179,17 +26179,17 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.201.000-0</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE RIO BUENO</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26199,17 +26199,17 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -26218,13 +26218,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2118.74</v>
+        <v>1297.17</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1426100-78-CM26</t>
+          <t>1079694-145-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26249,12 +26249,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26264,28 +26264,32 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K408" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2123.47</v>
+        <v>1405.56</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1079694-145-CM26</t>
+          <t>1426100-78-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26310,12 +26314,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26325,32 +26329,28 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K409" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1405.56</v>
+        <v>2123.47</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>3850-222-CM26</t>
+          <t>1426100-77-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26370,17 +26370,17 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>69.201.000-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO BUENO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26390,17 +26390,17 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -26409,13 +26409,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1297.17</v>
+        <v>2118.74</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1057548-533-CM26</t>
+          <t>1057548-536-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26455,17 +26455,17 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2994.31</v>
+        <v>4006.84</v>
       </c>
     </row>
     <row r="412">
@@ -26545,7 +26545,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1057548-536-CM26</t>
+          <t>1057548-533-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -26585,17 +26585,17 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -26604,7 +26604,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>4006.84</v>
+        <v>2994.31</v>
       </c>
     </row>
     <row r="414">
@@ -27825,7 +27825,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1057547-9370-CM26</t>
+          <t>1057553-226-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -27850,12 +27850,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.509-8</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -27865,28 +27865,32 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K433" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>6825.75</v>
+        <v>5069.4</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>1057553-226-CM26</t>
+          <t>1035685-201-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -27906,17 +27910,17 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>61.607.509-8</t>
+          <t>62.000.400-6</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE L</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -27945,13 +27949,13 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>5069.4</v>
+        <v>1337.97</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1035685-201-CM26</t>
+          <t>1057547-9370-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -27971,17 +27975,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>62.000.400-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE LA REGION DE LOS RIOS</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27991,26 +27995,22 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K435" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>1337.97</v>
+        <v>6825.75</v>
       </c>
     </row>
     <row r="436">
@@ -28337,7 +28337,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1491-52-CM26</t>
+          <t>3568-444-CM26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -28357,17 +28357,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -28377,28 +28377,32 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL MOLINA-LARSEN LIMITADA</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K441" t="inlineStr"/>
+          <t>77.983.294-5</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>3251.8</v>
+        <v>840.13</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>3568-444-CM26</t>
+          <t>1491-52-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -28418,17 +28422,17 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28438,32 +28442,28 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>COMERCIAL MOLINA-LARSEN LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>77.983.294-5</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>840.13</v>
+        <v>3251.8</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>707424-48-CM26</t>
+          <t>1340-328-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -28483,17 +28483,17 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -28522,13 +28522,13 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>28339.67</v>
+        <v>4152.21</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1340-328-CM26</t>
+          <t>707424-48-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -28548,17 +28548,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -28587,7 +28587,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>4152.21</v>
+        <v>28339.67</v>
       </c>
     </row>
     <row r="445">
@@ -28719,7 +28719,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>1057548-709-CM26</t>
+          <t>630424-438-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -28744,12 +28744,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.201.100-7</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -28759,17 +28759,17 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -28778,13 +28778,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>5189.62</v>
+        <v>7532.71</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>630424-438-CM26</t>
+          <t>1057548-709-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -28809,12 +28809,12 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>69.201.100-7</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO RANCO</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -28824,17 +28824,17 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
@@ -28843,7 +28843,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>7532.71</v>
+        <v>5189.62</v>
       </c>
     </row>
     <row r="449">
@@ -29170,7 +29170,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>5751-165-CM26</t>
+          <t>1057547-10198-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29190,17 +29190,17 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29210,32 +29210,28 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>COMERCIAL ARIA LIMITADA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>78.076.237-3</t>
-        </is>
-      </c>
-      <c r="K454" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>3205.42</v>
+        <v>6189.77</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1057547-10198-CM26</t>
+          <t>5751-165-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29255,17 +29251,17 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -29275,22 +29271,26 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>COMERCIAL ARIA LIMITADA</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K455" t="inlineStr"/>
+          <t>78.076.237-3</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>6189.77</v>
+        <v>3205.42</v>
       </c>
     </row>
     <row r="456">
@@ -29426,7 +29426,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2284-569-CM26</t>
+          <t>1057548-739-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -29446,17 +29446,17 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>69.200.100-1</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -29466,17 +29466,17 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -29485,7 +29485,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>7411.21</v>
+        <v>904.6</v>
       </c>
     </row>
     <row r="459">
@@ -29556,7 +29556,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>1057548-739-CM26</t>
+          <t>2284-569-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -29576,17 +29576,17 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.200.100-1</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD VALDIVIA</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -29596,17 +29596,17 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -29615,7 +29615,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>904.6</v>
+        <v>7411.21</v>
       </c>
     </row>
     <row r="461">
@@ -29942,7 +29942,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>5740-253-CM26</t>
+          <t>5740-256-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -29982,12 +29982,12 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K466" t="inlineStr">
@@ -30001,13 +30001,13 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1331.76</v>
+        <v>1658.46</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>5740-256-CM26</t>
+          <t>1723-427-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -30027,17 +30027,17 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>69.200.600-3</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -30047,12 +30047,12 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
@@ -30066,13 +30066,13 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>1658.46</v>
+        <v>1045.25</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>1723-427-CM26</t>
+          <t>2986-318-CM26</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -30112,12 +30112,12 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
@@ -30131,13 +30131,13 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>1045.25</v>
+        <v>2765.14</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2986-318-CM26</t>
+          <t>5740-253-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -30157,17 +30157,17 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>69.200.600-3</t>
+          <t>61.979.060-k</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS LAGOS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -30196,7 +30196,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2765.14</v>
+        <v>1331.76</v>
       </c>
     </row>
     <row r="470">
@@ -30267,7 +30267,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>1267885-679-CM26</t>
+          <t>1057547-11209-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -30292,12 +30292,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -30307,12 +30307,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>FLEXING CHILE SPA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>76.592.530-4</t>
+          <t>77.338.250-6</t>
         </is>
       </c>
       <c r="K471" t="inlineStr"/>
@@ -30322,13 +30322,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>5325.05</v>
+        <v>3561.02</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1057547-11209-CM26</t>
+          <t>2908-209-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -30353,12 +30353,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -30368,28 +30368,32 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K472" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>3561.02</v>
+        <v>1158.81</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2908-209-CM26</t>
+          <t>1267885-679-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -30414,12 +30418,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -30429,26 +30433,22 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>FLEXING CHILE SPA</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
-        </is>
-      </c>
-      <c r="K473" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.592.530-4</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>1158.81</v>
+        <v>5325.05</v>
       </c>
     </row>
     <row r="474">
@@ -30836,7 +30836,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1057547-12125-CM26</t>
+          <t>593649-11-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -30861,12 +30861,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -30876,28 +30876,32 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
-        </is>
-      </c>
-      <c r="K480" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>20561.39</v>
+        <v>1534.67</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>593649-11-CM26</t>
+          <t>1057547-12125-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -30922,12 +30926,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -30937,32 +30941,28 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K481" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1534.67</v>
+        <v>20561.39</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1057547-12207-CM26</t>
+          <t>4062-578-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -30987,12 +30987,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -31021,13 +31021,13 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>3794.12</v>
+        <v>2048.96</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>1057547-12208-CM26</t>
+          <t>1057547-12207-CM26</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -31067,28 +31067,32 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>78.809.560-0</t>
-        </is>
-      </c>
-      <c r="K483" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>4084.95</v>
+        <v>3794.12</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>4062-578-CM26</t>
+          <t>1057547-12208-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31113,12 +31117,12 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -31128,26 +31132,22 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA Y COMERCIAL DIMAK LIMITADA</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K484" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.809.560-0</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>2048.96</v>
+        <v>4084.95</v>
       </c>
     </row>
     <row r="485">
@@ -32315,7 +32315,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -32803,7 +32803,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>3986-310-CM26</t>
+          <t>1057547-13658-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -32823,17 +32823,17 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>69.200.200-8</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CORRAL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -32843,32 +32843,28 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
-        </is>
-      </c>
-      <c r="K511" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>2222.9</v>
+        <v>2194.41</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1057547-13658-CM26</t>
+          <t>3986-310-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -32888,17 +32884,17 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>69.200.200-8</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>MUNICIPALIDAD DE CORRAL</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -32908,28 +32904,32 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K512" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2194.41</v>
+        <v>2222.9</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>3545-235-CM26</t>
+          <t>5538-261-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -32954,12 +32954,12 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>65.273.020-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -32969,17 +32969,17 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -32988,7 +32988,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2282.08</v>
+        <v>4097.28</v>
       </c>
     </row>
     <row r="514">
@@ -33120,7 +33120,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>5538-261-CM26</t>
+          <t>3545-235-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33145,12 +33145,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>65.273.020-5</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -33160,17 +33160,17 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -33179,7 +33179,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>4097.28</v>
+        <v>2282.08</v>
       </c>
     </row>
     <row r="517">
@@ -34111,7 +34111,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -34993,7 +34993,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>1218393-453-CM26</t>
+          <t>1057548-1100-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35018,12 +35018,12 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>53.335.808-K</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>CONSULTORIO EXTERNO VALDIVIA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -35052,13 +35052,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>4355.58</v>
+        <v>1512.36</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>5538-305-CM26</t>
+          <t>3789-595-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35083,12 +35083,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -35098,28 +35098,32 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MONARQUÍA SPA</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K546" t="inlineStr"/>
+          <t>78.199.695-5</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>9626.91</v>
+        <v>4270.22</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>1057548-1100-CM26</t>
+          <t>3789-594-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35139,17 +35143,17 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -35159,12 +35163,12 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
@@ -35178,13 +35182,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>1512.36</v>
+        <v>3509.83</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>3789-595-CM26</t>
+          <t>5538-305-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -35209,12 +35213,12 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -35224,32 +35228,28 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>MONARQUÍA SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>78.199.695-5</t>
-        </is>
-      </c>
-      <c r="K548" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr"/>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>4270.22</v>
+        <v>9626.91</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>3789-594-CM26</t>
+          <t>1218393-453-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -35269,17 +35269,17 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>53.335.808-K</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>CONSULTORIO EXTERNO VALDIVIA</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -35289,12 +35289,12 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
@@ -35308,7 +35308,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>3509.83</v>
+        <v>4355.58</v>
       </c>
     </row>
     <row r="550">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1057547-15358-CM26</t>
+          <t>1057552-1003-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -35717,12 +35717,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.508-K</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -35751,13 +35751,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>5373.95</v>
+        <v>3313.24</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1057547-15359-CM26</t>
+          <t>1057547-15332-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -35812,13 +35812,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>2540.99</v>
+        <v>6337.01</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1057552-1003-CM26</t>
+          <t>1057547-15358-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -35843,12 +35843,12 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>61.607.508-K</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL DE R</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -35877,13 +35877,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>3313.24</v>
+        <v>5373.95</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>1057547-15332-CM26</t>
+          <t>1057547-15359-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -35938,13 +35938,13 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>6337.01</v>
+        <v>2540.99</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>1067355-503-CM26</t>
+          <t>1057547-15378-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -35969,12 +35969,12 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>61.980.670-0</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -35984,32 +35984,28 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOC COMERCIAL CINTEC LIMITADA</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K560" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.338.250-6</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr"/>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>933.9</v>
+        <v>3535.81</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>1057548-1147-CM26</t>
+          <t>1067355-503-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -36034,12 +36030,12 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>61.607.503-9</t>
+          <t>61.980.670-0</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -36049,17 +36045,17 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
@@ -36068,13 +36064,13 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>2511.1</v>
+        <v>933.9</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>1057547-15378-CM26</t>
+          <t>1057548-1147-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36099,12 +36095,12 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>61.607.503-9</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL LA U</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -36114,28 +36110,32 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>SOC COMERCIAL CINTEC LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>77.338.250-6</t>
-        </is>
-      </c>
-      <c r="K562" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>3535.81</v>
+        <v>2511.1</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>5740-389-CM26</t>
+          <t>1057547-15455-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36155,17 +36155,17 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>61.979.060-k</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -36175,32 +36175,28 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
-        </is>
-      </c>
-      <c r="K563" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr"/>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>1686.08</v>
+        <v>942.7</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>5538-310-CM26</t>
+          <t>5538-309-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -36240,12 +36236,12 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
@@ -36259,13 +36255,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>1432.87</v>
+        <v>9438.049999999999</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>5538-312-CM26</t>
+          <t>5538-310-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -36305,17 +36301,17 @@
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
@@ -36324,13 +36320,13 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1143.58</v>
+        <v>1432.87</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>1057547-15455-CM26</t>
+          <t>5538-312-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -36350,17 +36346,17 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>61.607.502-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -36370,22 +36366,221 @@
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
-        </is>
-      </c>
-      <c r="K566" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>942.7</v>
+        <v>1143.58</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>5740-389-CM26</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>61.979.060-k</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M567" s="2" t="n">
+        <v>1686.08</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>1067355-502-CM26</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>61.980.670-0</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>HOSPITAL SANTA ELISA DE SAN JOSE DE LA MARIQUINA</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M568" s="2" t="n">
+        <v>7228.95</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>5538-317-CM26</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>PAPELES AUSTRAL SPA</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>77.404.653-4</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M569" s="2" t="n">
+        <v>1606.79</v>
       </c>
     </row>
   </sheetData>
